--- a/results/Int Task Remove ACC -0.2/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_8_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6383872529427328</v>
+        <v>0.6269268731130013</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6383872529427328</v>
+        <v>0.629904554691766</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.644814072577089</v>
+        <v>0.629904554691766</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6414484362656518</v>
+        <v>0.6289424081903014</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6354210645815624</v>
+        <v>0.6372196358573378</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6354210645815624</v>
+        <v>0.6346202922373401</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6259560480594757</v>
+        <v>0.6175310504519415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6177498906971551</v>
+        <v>0.637485621750234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6234190961921329</v>
+        <v>0.6356438922696149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6224367779210129</v>
+        <v>0.6235382503663756</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6268778510216297</v>
+        <v>0.6247251009995816</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6269902030875004</v>
+        <v>0.6204683884913955</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6269902030875004</v>
+        <v>0.6204683884913955</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6139540796700461</v>
+        <v>0.6343245178008831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6150794767724418</v>
+        <v>0.6337310924842801</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6172284739071123</v>
+        <v>0.6337310924842801</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6189674680957662</v>
+        <v>0.6378860079223452</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6192949075194728</v>
+        <v>0.6250534786451326</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6256084368661139</v>
+        <v>0.6267732392859757</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6241450453442617</v>
+        <v>0.6264765266276742</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6241450453442617</v>
+        <v>0.6347537542947105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6241450453442617</v>
+        <v>0.6378447261611903</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6269181945609403</v>
+        <v>0.6363198811085279</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6259051495244153</v>
+        <v>0.6363198811085279</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6247490256566146</v>
+        <v>0.6362277008123125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6295175381809379</v>
+        <v>0.6362277008123125</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6214227946626436</v>
+        <v>0.6384275964820434</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6301513070368514</v>
+        <v>0.6273858981503895</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6015796372083773</v>
+        <v>0.6266590107764161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5876524375941741</v>
+        <v>0.6361249655203471</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5886127076519497</v>
+        <v>0.6398804330081456</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6062522165491074</v>
+        <v>0.6358282528620458</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6219510135610585</v>
+        <v>0.6357879093227352</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6224013600463857</v>
+        <v>0.630324174411688</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6254423715996495</v>
+        <v>0.6452827143883826</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6260972504470628</v>
+        <v>0.6125397102395655</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.61302758559867</v>
+        <v>0.602727082524117</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6038391099652295</v>
+        <v>0.5757349091707432</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6045756141131082</v>
+        <v>0.5893337311393954</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6172036110282348</v>
+        <v>0.5960668802059584</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6099558472800011</v>
+        <v>0.5659654396601386</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6116237711639393</v>
+        <v>0.5654334678743458</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6216611030111292</v>
+        <v>0.5596615270874029</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6271968464487365</v>
+        <v>0.5610020115476344</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6418912769762236</v>
+        <v>0.5608012320729261</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6622049526854724</v>
+        <v>0.5650473895853623</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6330792628578612</v>
+        <v>0.5720455863229772</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6222439733319822</v>
+        <v>0.5852977353201119</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.627073939387116</v>
+        <v>0.5944660391838972</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6166151113763152</v>
+        <v>0.5929210223615794</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6179757676062021</v>
+        <v>0.5914480140658219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6155915113440403</v>
+        <v>0.5781334733160325</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6217840100727497</v>
+        <v>0.5776725718349556</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6203619003120526</v>
+        <v>0.5787259604107911</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.613373320348343</v>
+        <v>0.5735272731707958</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6368183114633822</v>
+        <v>0.5860755212291457</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6244774104326516</v>
+        <v>0.6024456159707875</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6593827813774222</v>
+        <v>0.6028037821598993</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6534801931986423</v>
+        <v>0.5932053035804422</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6524258664009622</v>
+        <v>0.5767920506339564</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5451706907001574</v>
+        <v>0.5556189637152084</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5532539410008576</v>
+        <v>0.53131245039152</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5528035945155304</v>
+        <v>0.5425614957507933</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5443938430129681</v>
+        <v>0.5426844028124138</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5398711446118858</v>
+        <v>0.5548726082379631</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5398711446118858</v>
+        <v>0.5549955152995836</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5279815282883269</v>
+        <v>0.5325058685776369</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5224966833857799</v>
+        <v>0.5222112293896116</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.512648403240243</v>
+        <v>0.5205740322710786</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5099174740065637</v>
+        <v>0.5277988095841237</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5207834902978479</v>
+        <v>0.527236111032926</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5183685072702811</v>
+        <v>0.5236054270504369</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5186450481589273</v>
+        <v>0.5243524861940656</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5206816932277271</v>
+        <v>0.5243524861940656</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.52839716056541</v>
+        <v>0.519603207217553</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5404711374813997</v>
+        <v>0.524064452087825</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5258217416024454</v>
+        <v>0.5123380863651972</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.517983367203142</v>
+        <v>0.5137400243562391</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5226798712009052</v>
+        <v>0.5163691565197974</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4950654222092122</v>
+        <v>0.5129613002253609</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4994881999838626</v>
+        <v>0.512572407270844</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4895815155285098</v>
+        <v>0.512572407270844</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4987718676056391</v>
+        <v>0.512572407270844</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4993960196876472</v>
+        <v>0.5170749339022711</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4993960196876472</v>
+        <v>0.5127279175415586</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4989149464369149</v>
+        <v>0.5055453602115128</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5021077153735155</v>
+        <v>0.5031707207232564</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5021384421389206</v>
+        <v>0.5027203742379293</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5021384421389206</v>
+        <v>0.5086546274039589</v>
       </c>
     </row>
   </sheetData>
